--- a/Redes.xlsx
+++ b/Redes.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Chaires\Documents\Dirección de Planeación, Evaluación e Innovación\9- Tablero Redes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC32EC30-E551-4709-A334-B8F4992A1534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3790E54D-EF4E-4228-A144-E26749BB8DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Resumen" sheetId="1" r:id="rId1"/>
     <sheet name="02_Publicaciones" sheetId="2" r:id="rId2"/>
     <sheet name="03_Cuentas" sheetId="3" r:id="rId3"/>
     <sheet name="04_Destacada" sheetId="4" r:id="rId4"/>
+    <sheet name="Historico" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="105">
   <si>
     <t>Responsable</t>
   </si>
@@ -79,21 +80,6 @@
   </si>
   <si>
     <t>descripcion</t>
-  </si>
-  <si>
-    <t>reacciones</t>
-  </si>
-  <si>
-    <t>comentarios</t>
-  </si>
-  <si>
-    <t>reposts</t>
-  </si>
-  <si>
-    <t>enviados</t>
-  </si>
-  <si>
-    <t>visualizaciones</t>
   </si>
   <si>
     <t>enlace</t>
@@ -409,12 +395,47 @@
   <si>
     <t>fecha_reporte</t>
   </si>
+  <si>
+    <r>
+      <t>#EnVivo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF080809"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> | Nos encontramos en una edición más de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0064D1"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+      </rPr>
+      <t>#AyudamosDeCerca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF080809"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> desde Apodaca, donde acercaremos nuestros programas y atención directa a su comunidad.</t>
+    </r>
+  </si>
+  <si>
+    <t>fecha_corte_anterior</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,6 +486,43 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0064D1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF080809"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0C1014"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -502,7 +560,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -522,8 +580,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -839,18 +905,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C846309B-E716-4A90-9426-BA939BBB812D}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -862,12 +929,15 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>101</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="3">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -879,6 +949,9 @@
         <v>5</v>
       </c>
       <c r="E2" s="3">
+        <v>46265</v>
+      </c>
+      <c r="F2" s="3">
         <v>46261</v>
       </c>
     </row>
@@ -889,20 +962,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72FCB01-E2AD-44E8-AD5B-2B17A2E2EE2B}">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="8" customWidth="1"/>
     <col min="2" max="5" width="11.42578125" style="8"/>
     <col min="6" max="6" width="25.85546875" style="8" customWidth="1"/>
     <col min="7" max="7" width="135.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="11.42578125" style="8"/>
-    <col min="12" max="12" width="14.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="97.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.42578125" style="8"/>
+    <col min="8" max="8" width="97.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.42578125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:8">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
@@ -927,858 +998,1254 @@
       <c r="H1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="19.5">
+      <c r="A2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="20.25">
+      <c r="A3" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="39">
+      <c r="A4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="78">
+      <c r="A5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="39">
+      <c r="A6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="19.5">
+      <c r="A7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="F7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" ht="19.5">
+      <c r="A8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" ht="19.5">
+      <c r="A9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" ht="20.25">
+      <c r="A10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="39">
+      <c r="A11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="58.5">
+      <c r="A12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.25">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="19.5">
+      <c r="A14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="19.5">
+      <c r="A15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="58.5">
+      <c r="A16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="117">
+      <c r="A17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="39">
+      <c r="A18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="58.5">
+      <c r="A19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="G19" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="58.5">
+      <c r="A20" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="39">
+      <c r="A21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="19.5">
+      <c r="A22" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="58.5">
+      <c r="A23" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="19.5">
+      <c r="A24" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:8" ht="19.5">
+      <c r="A25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:8" ht="19.5">
+      <c r="A26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="10">
+        <v>46261</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:8" ht="19.5">
+      <c r="A27" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="19.5">
-      <c r="A2" s="8" t="s">
+    <row r="28" spans="1:8" ht="20.25">
+      <c r="A28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="B28" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="39">
+      <c r="A29" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="78">
+      <c r="A30" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="39">
+      <c r="A31" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="19.5">
+      <c r="A32" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="1:8" ht="19.5">
+      <c r="A33" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="1:8" ht="19.5">
+      <c r="A34" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="1:8" ht="20.25">
+      <c r="A35" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="B35" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="39">
+      <c r="A36" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="58.5">
+      <c r="A37" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="20.25">
+      <c r="A38" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="19.5">
+      <c r="A39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="19.5">
+      <c r="A40" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1400</v>
-      </c>
-      <c r="I2" s="5">
-        <v>1300</v>
-      </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="M2" s="8" t="s">
+      <c r="F40" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="58.5">
+      <c r="A41" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="117">
+      <c r="A42" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="39">
+      <c r="A43" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="20.25">
-      <c r="A3" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="G43" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="58.5">
+      <c r="A44" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="58.5">
+      <c r="A45" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="39">
+      <c r="A46" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="19.5">
+      <c r="A47" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="58.5">
+      <c r="A48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="19.5">
+      <c r="A49" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" s="5">
-        <v>569</v>
-      </c>
-      <c r="I3" s="5">
-        <v>255</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1300</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="M3" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="39">
-      <c r="A4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="5">
-        <v>414</v>
-      </c>
-      <c r="I4" s="5">
-        <v>136</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1900</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="M4" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="78">
-      <c r="A5" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="5">
-        <v>337</v>
-      </c>
-      <c r="I5" s="5">
-        <v>135</v>
-      </c>
-      <c r="J5" s="5">
-        <v>2100</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="M5" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="39">
-      <c r="A6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="5">
-        <v>167</v>
-      </c>
-      <c r="I6" s="5">
-        <v>38</v>
-      </c>
-      <c r="J6" s="5">
-        <v>25</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="M6" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="19.5">
-      <c r="A7" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="17"/>
-    </row>
-    <row r="8" spans="1:13" ht="19.5">
-      <c r="A8" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="17"/>
-    </row>
-    <row r="9" spans="1:13" ht="19.5">
-      <c r="A9" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="17"/>
-    </row>
-    <row r="10" spans="1:13" ht="20.25">
-      <c r="A10" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="17"/>
-    </row>
-    <row r="11" spans="1:13" ht="39">
-      <c r="A11" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="H11" s="5">
-        <v>100</v>
-      </c>
-      <c r="I11" s="5">
-        <v>9</v>
-      </c>
-      <c r="J11" s="5">
-        <v>6</v>
-      </c>
-      <c r="K11" s="5">
-        <v>2</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="58.5">
-      <c r="A12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="5">
-        <v>66</v>
-      </c>
-      <c r="I12" s="5">
-        <v>3</v>
-      </c>
-      <c r="J12" s="5">
-        <v>6</v>
-      </c>
-      <c r="K12" s="5"/>
-      <c r="M12" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="20.25">
-      <c r="A13" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="5">
-        <v>58</v>
-      </c>
-      <c r="I13" s="5">
-        <v>10</v>
-      </c>
-      <c r="J13" s="5">
-        <v>6</v>
-      </c>
-      <c r="K13" s="5">
-        <v>1</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="19.5">
-      <c r="A14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="5">
-        <v>223</v>
-      </c>
-      <c r="I14" s="5">
-        <v>72</v>
-      </c>
-      <c r="J14" s="5">
-        <v>12</v>
-      </c>
-      <c r="K14" s="5"/>
-      <c r="M14" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="19.5">
-      <c r="A15" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="5">
-        <v>185</v>
-      </c>
-      <c r="I15" s="5">
-        <v>27</v>
-      </c>
-      <c r="J15" s="5">
-        <v>6</v>
-      </c>
-      <c r="K15" s="18"/>
-      <c r="M15" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="58.5">
-      <c r="A16" s="8" t="s">
+      <c r="G49" s="6"/>
+    </row>
+    <row r="50" spans="1:7" ht="19.5">
+      <c r="A50" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="5">
-        <v>131</v>
-      </c>
-      <c r="I16" s="5">
-        <v>19</v>
-      </c>
-      <c r="J16" s="5">
-        <v>47</v>
-      </c>
-      <c r="K16" s="18"/>
-      <c r="M16" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="117">
-      <c r="A17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="5">
-        <v>29</v>
-      </c>
-      <c r="I17" s="5">
-        <v>2</v>
-      </c>
-      <c r="J17" s="5">
-        <v>1</v>
-      </c>
-      <c r="K17" s="18"/>
-      <c r="M17" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="39">
-      <c r="A18" s="8" t="s">
+      <c r="B50" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="6"/>
+    </row>
+    <row r="51" spans="1:7" ht="19.5">
+      <c r="A51" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="5">
-        <v>25</v>
-      </c>
-      <c r="I18" s="5">
-        <v>2</v>
-      </c>
-      <c r="J18" s="5">
-        <v>11</v>
-      </c>
-      <c r="K18" s="18"/>
-      <c r="M18" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="58.5">
-      <c r="A19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="5">
-        <v>19</v>
-      </c>
-      <c r="I19" s="5">
-        <v>1</v>
-      </c>
-      <c r="J19" s="5">
-        <v>4</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="M19" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="58.5">
-      <c r="A20" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="5">
-        <v>35</v>
-      </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5">
-        <v>3</v>
-      </c>
-      <c r="K20" s="5">
-        <v>4</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="39">
-      <c r="A21" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="H21" s="5">
-        <v>32</v>
-      </c>
-      <c r="I21" s="5">
-        <v>3</v>
-      </c>
-      <c r="J21" s="5">
-        <v>1</v>
-      </c>
-      <c r="K21" s="5">
-        <v>1</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="19.5">
-      <c r="A22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H22" s="5">
-        <v>22</v>
-      </c>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="M22" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="58.5">
-      <c r="A23" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="5">
+      <c r="B51" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5">
-        <v>1</v>
-      </c>
-      <c r="K23" s="5">
-        <v>1</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="19.5">
-      <c r="A24" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-    </row>
-    <row r="25" spans="1:13" ht="19.5">
-      <c r="A25" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-    </row>
-    <row r="26" spans="1:13" ht="19.5">
-      <c r="A26" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="10">
-        <v>46261</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
+      <c r="F51" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="6"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M26">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H26">
     <sortCondition ref="C2:C26"/>
     <sortCondition ref="D2:D26"/>
-    <sortCondition descending="1" ref="H2:H26"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="M6" r:id="rId1" xr:uid="{261581AD-DFF1-4EAF-833B-95FCE5C2B91E}"/>
-    <hyperlink ref="M11" r:id="rId2" xr:uid="{C7DBB0BB-2BE7-4A3A-9678-05B590B031E9}"/>
-    <hyperlink ref="M12" r:id="rId3" xr:uid="{02B8A9A4-1CA6-4A42-9749-8D7AF3431544}"/>
+    <hyperlink ref="H6" r:id="rId1" xr:uid="{261581AD-DFF1-4EAF-833B-95FCE5C2B91E}"/>
+    <hyperlink ref="H11" r:id="rId2" xr:uid="{C7DBB0BB-2BE7-4A3A-9678-05B590B031E9}"/>
+    <hyperlink ref="H12" r:id="rId3" xr:uid="{02B8A9A4-1CA6-4A42-9749-8D7AF3431544}"/>
+    <hyperlink ref="H31" r:id="rId4" xr:uid="{F4FA72A5-647B-4B8A-9AE2-704FA46838B2}"/>
+    <hyperlink ref="H36" r:id="rId5" xr:uid="{EA2D880C-759A-4890-BBCA-486AE06E029F}"/>
+    <hyperlink ref="H37" r:id="rId6" xr:uid="{B8FF44E5-052E-4C85-9346-BF1E5296B6AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1800,10 +2267,10 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19.5">
@@ -1811,10 +2278,10 @@
         <v>46261</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D2" s="5">
         <v>205000</v>
@@ -1825,10 +2292,10 @@
         <v>46261</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D3" s="5">
         <v>17300</v>
@@ -1839,10 +2306,10 @@
         <v>46261</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5">
         <v>234000</v>
@@ -1853,10 +2320,10 @@
         <v>46261</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5">
         <v>39900</v>
@@ -1893,13 +2360,13 @@
         <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5">
@@ -1907,19 +2374,19 @@
         <v>46261</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5">
@@ -1927,23 +2394,696 @@
         <v>46261</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FD25CDE-4DA6-4E43-93E0-F613641E2B24}">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.28515625" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="17" customFormat="1" ht="14.25">
+      <c r="A1" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A2" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A3" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A4" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A5" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A6" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A7" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="18"/>
+    </row>
+    <row r="8" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A8" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="18"/>
+    </row>
+    <row r="9" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A9" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="21"/>
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A10" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A11" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A12" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A13" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A14" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A15" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A16" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A17" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A18" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A19" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A20" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A21" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A22" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A23" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A24" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A25" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="21"/>
+      <c r="H25" s="18"/>
+    </row>
+    <row r="26" spans="1:8" s="22" customFormat="1" ht="16.5">
+      <c r="A26" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="19">
+        <v>46261</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="21"/>
+      <c r="H26" s="18"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" r:id="rId1" xr:uid="{B35D16F2-CAB4-4F4D-B238-8C19A4AE8DA7}"/>
+    <hyperlink ref="H11" r:id="rId2" xr:uid="{6CF6F96F-6D4A-4D54-A8F4-EA19602C0326}"/>
+    <hyperlink ref="H12" r:id="rId3" xr:uid="{269222A1-6B95-41E4-9CE1-56CB3B1DEA5A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+</worksheet>
 </file>
--- a/Redes.xlsx
+++ b/Redes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Chaires\Documents\Dirección de Planeación, Evaluación e Innovación\9- Tablero Redes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3790E54D-EF4E-4228-A144-E26749BB8DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AFE292-50AA-477F-9219-0FBF8DF505E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
+    <workbookView xWindow="4575" yWindow="4575" windowWidth="21510" windowHeight="7845" xr2:uid="{7FB54C1C-01EA-46D2-B3AA-10A0B7D9ACCD}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Resumen" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="106">
   <si>
     <t>Responsable</t>
   </si>
@@ -221,9 +221,6 @@
   </si>
   <si>
     <t>seguidores</t>
-  </si>
-  <si>
-    <t>crecimiento dia</t>
   </si>
   <si>
     <t>motivo</t>
@@ -429,6 +426,12 @@
   </si>
   <si>
     <t>fecha_corte_anterior</t>
+  </si>
+  <si>
+    <t>Mónica Oyervides</t>
+  </si>
+  <si>
+    <t>seguidores_corte_actual</t>
   </si>
 </sst>
 </file>
@@ -905,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C846309B-E716-4A90-9426-BA939BBB812D}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -917,41 +920,57 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="3">
+        <v>46265</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="3">
-        <v>46265</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="3">
         <v>46265</v>
       </c>
-      <c r="F2" s="3">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="3">
         <v>46261</v>
       </c>
     </row>
@@ -962,7 +981,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72FCB01-E2AD-44E8-AD5B-2B17A2E2EE2B}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="8" customWidth="1"/>
@@ -1019,7 +1038,7 @@
         <v>43</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>18</v>
@@ -1045,10 +1064,10 @@
         <v>22</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="39">
@@ -1071,10 +1090,10 @@
         <v>22</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="78">
@@ -1097,10 +1116,10 @@
         <v>45</v>
       </c>
       <c r="G5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39">
@@ -1123,10 +1142,10 @@
         <v>44</v>
       </c>
       <c r="G6" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="19.5">
@@ -1212,7 +1231,7 @@
         <v>42</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39">
@@ -1235,10 +1254,10 @@
         <v>22</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="58.5">
@@ -1261,10 +1280,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20.25">
@@ -1287,10 +1306,10 @@
         <v>44</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="19.5">
@@ -1313,10 +1332,10 @@
         <v>24</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.5">
@@ -1339,10 +1358,10 @@
         <v>22</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="58.5">
@@ -1365,10 +1384,10 @@
         <v>22</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="117">
@@ -1391,10 +1410,10 @@
         <v>21</v>
       </c>
       <c r="G17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39">
@@ -1417,10 +1436,10 @@
         <v>23</v>
       </c>
       <c r="G18" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="58.5">
@@ -1443,10 +1462,10 @@
         <v>17</v>
       </c>
       <c r="G19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="58.5">
@@ -1469,10 +1488,10 @@
         <v>22</v>
       </c>
       <c r="G20" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39">
@@ -1495,10 +1514,10 @@
         <v>23</v>
       </c>
       <c r="G21" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="19.5">
@@ -1521,10 +1540,10 @@
         <v>24</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="58.5">
@@ -1547,10 +1566,10 @@
         <v>17</v>
       </c>
       <c r="G23" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="19.5">
@@ -1636,7 +1655,7 @@
         <v>43</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>18</v>
@@ -1662,10 +1681,10 @@
         <v>22</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="39">
@@ -1688,10 +1707,10 @@
         <v>22</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="78">
@@ -1714,10 +1733,10 @@
         <v>45</v>
       </c>
       <c r="G30" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="39">
@@ -1740,10 +1759,10 @@
         <v>44</v>
       </c>
       <c r="G31" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="19.5">
@@ -1829,7 +1848,7 @@
         <v>42</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="39">
@@ -1852,10 +1871,10 @@
         <v>22</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="58.5">
@@ -1878,10 +1897,10 @@
         <v>45</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="20.25">
@@ -1904,10 +1923,10 @@
         <v>44</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="19.5">
@@ -1930,10 +1949,10 @@
         <v>24</v>
       </c>
       <c r="G39" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="19.5">
@@ -1956,10 +1975,10 @@
         <v>22</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="58.5">
@@ -1982,10 +2001,10 @@
         <v>22</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="117">
@@ -2008,10 +2027,10 @@
         <v>21</v>
       </c>
       <c r="G42" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="39">
@@ -2034,10 +2053,10 @@
         <v>23</v>
       </c>
       <c r="G43" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="58.5">
@@ -2060,10 +2079,10 @@
         <v>17</v>
       </c>
       <c r="G44" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H44" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="58.5">
@@ -2086,10 +2105,10 @@
         <v>22</v>
       </c>
       <c r="G45" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H45" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="39">
@@ -2112,10 +2131,10 @@
         <v>23</v>
       </c>
       <c r="G46" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H46" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="19.5">
@@ -2138,10 +2157,10 @@
         <v>24</v>
       </c>
       <c r="G47" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H47" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="58.5">
@@ -2164,10 +2183,10 @@
         <v>17</v>
       </c>
       <c r="G48" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H48" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="19.5">
@@ -2232,6 +2251,92 @@
         <v>17</v>
       </c>
       <c r="G51" s="6"/>
+    </row>
+    <row r="52" spans="1:7" ht="58.5">
+      <c r="A52" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="19.5">
+      <c r="A53" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C53" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G53" s="6"/>
+    </row>
+    <row r="54" spans="1:7" ht="19.5">
+      <c r="A54" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="6"/>
+    </row>
+    <row r="55" spans="1:7" ht="19.5">
+      <c r="A55" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" s="6"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H26">
@@ -2253,7 +2358,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC9B935-22C6-4521-930C-0B9B2B3FDA48}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2270,7 +2375,7 @@
         <v>59</v>
       </c>
       <c r="E1" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19.5">
@@ -2286,6 +2391,9 @@
       <c r="D2" s="5">
         <v>205000</v>
       </c>
+      <c r="E2" s="5">
+        <v>205800</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="19.5">
       <c r="A3" s="1">
@@ -2300,6 +2408,9 @@
       <c r="D3" s="5">
         <v>17300</v>
       </c>
+      <c r="E3" s="5">
+        <v>17350</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="19.5">
       <c r="A4" s="1">
@@ -2314,6 +2425,9 @@
       <c r="D4" s="5">
         <v>234000</v>
       </c>
+      <c r="E4" s="5">
+        <v>234100</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="19.5">
       <c r="A5" s="1">
@@ -2327,6 +2441,43 @@
       </c>
       <c r="D5" s="5">
         <v>39900</v>
+      </c>
+      <c r="E5" s="5">
+        <v>40100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="19.5">
+      <c r="A6" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5">
+        <v>234000</v>
+      </c>
+      <c r="E6" s="5">
+        <v>234100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="19.5">
+      <c r="A7" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="5">
+        <v>39900</v>
+      </c>
+      <c r="E7" s="5">
+        <v>40100</v>
       </c>
     </row>
   </sheetData>
@@ -2336,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0E442DF-0272-4E03-BC5B-4CC7C5C08958}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="11.42578125" style="4"/>
@@ -2360,13 +2511,13 @@
         <v>6</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5">
@@ -2383,10 +2534,10 @@
         <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5">
@@ -2403,10 +2554,30 @@
         <v>50</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>99</v>
+    </row>
+    <row r="4" spans="1:7" ht="19.5">
+      <c r="A4" s="15">
+        <v>46261</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2473,7 +2644,7 @@
         <v>43</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H2" s="18" t="s">
         <v>18</v>
@@ -2499,10 +2670,10 @@
         <v>22</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2525,10 +2696,10 @@
         <v>22</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2551,10 +2722,10 @@
         <v>45</v>
       </c>
       <c r="G5" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="18" t="s">
         <v>69</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2577,10 +2748,10 @@
         <v>44</v>
       </c>
       <c r="G6" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="24" t="s">
         <v>65</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2669,7 +2840,7 @@
         <v>42</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H10" s="18"/>
     </row>
@@ -2693,10 +2864,10 @@
         <v>22</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2719,10 +2890,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2745,10 +2916,10 @@
         <v>44</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2771,10 +2942,10 @@
         <v>24</v>
       </c>
       <c r="G14" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>81</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2797,10 +2968,10 @@
         <v>22</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2823,10 +2994,10 @@
         <v>22</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2849,10 +3020,10 @@
         <v>21</v>
       </c>
       <c r="G17" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="18" t="s">
         <v>75</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2875,10 +3046,10 @@
         <v>23</v>
       </c>
       <c r="G18" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="18" t="s">
         <v>79</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2901,10 +3072,10 @@
         <v>17</v>
       </c>
       <c r="G19" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="18" t="s">
         <v>73</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2927,10 +3098,10 @@
         <v>22</v>
       </c>
       <c r="G20" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="18" t="s">
         <v>91</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2953,10 +3124,10 @@
         <v>23</v>
       </c>
       <c r="G21" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="18" t="s">
         <v>93</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -2979,10 +3150,10 @@
         <v>24</v>
       </c>
       <c r="G22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H22" s="18" t="s">
         <v>95</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="22" customFormat="1" ht="16.5">
@@ -3005,10 +3176,10 @@
         <v>17</v>
       </c>
       <c r="G23" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="18" t="s">
         <v>89</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:8" s="22" customFormat="1" ht="16.5">

--- a/Redes.xlsx
+++ b/Redes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Chaires\Documents\Dirección de Planeación, Evaluación e Innovación\9- Tablero Redes\redes 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBF58EE-7FF8-4E3E-BA0A-419C80C13D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3A2D3C-CB7F-461E-8C1A-5E175E810C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -545,7 +545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -558,7 +558,7 @@
         <v>31</v>
       </c>
       <c r="B5" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -566,7 +566,7 @@
         <v>32</v>
       </c>
       <c r="B6" s="2">
-        <v>46261</v>
+        <v>46265</v>
       </c>
     </row>
   </sheetData>
